--- a/artfynd/A 388-2026 artfynd.xlsx
+++ b/artfynd/A 388-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109890408</v>
+        <v>109890399</v>
       </c>
       <c r="B2" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +703,16 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657510.5131193234</v>
+        <v>657625</v>
       </c>
       <c r="R2" t="n">
-        <v>7428378.070105317</v>
+        <v>7428472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +757,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109890417</v>
+        <v>109890400</v>
       </c>
       <c r="B3" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,22 +833,33 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Liebben, 2,5 km NO om Tjåmotis, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657661.4304484975</v>
+        <v>657548</v>
       </c>
       <c r="R3" t="n">
-        <v>7428463.090193649</v>
+        <v>7428413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,24 +889,14 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>För sammanlagda antal, se polygonen för hela lokalen</t>
+          <t>Samtliga florala. För sammanlagda antal, se polygonen för hela lokalen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,6 +905,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -947,15 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109890409</v>
+        <v>109890401</v>
       </c>
       <c r="B4" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +966,16 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -992,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>657523.3785348632</v>
+        <v>657538</v>
       </c>
       <c r="R4" t="n">
-        <v>7428468.452452422</v>
+        <v>7428404</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,24 +1020,14 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>För sammanlagda antal, se polygonen för hela lokalen</t>
+          <t>1 floral + 1 vegetativ. För sammanlagda antal, se polygonen för hela lokalen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1086,12 +1071,7 @@
         <v>109890402</v>
       </c>
       <c r="B5" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>657529.3880505699</v>
+        <v>657529</v>
       </c>
       <c r="R5" t="n">
-        <v>7428405.504898123</v>
+        <v>7428406</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1170,19 +1150,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1228,15 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109890400</v>
+        <v>109890403</v>
       </c>
       <c r="B6" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,33 +1226,22 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Liebben, 2,5 km NO om Tjåmotis, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>657548.2669168669</v>
+        <v>657429</v>
       </c>
       <c r="R6" t="n">
-        <v>7428412.496317334</v>
+        <v>7428381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1317,24 +1271,14 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Samtliga florala. För sammanlagda antal, se polygonen för hela lokalen</t>
+          <t>För sammanlagda antal, se polygonen för hela lokalen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1343,7 +1287,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1376,15 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109890412</v>
+        <v>109890404</v>
       </c>
       <c r="B7" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1421,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>657551.6232128849</v>
+        <v>657457</v>
       </c>
       <c r="R7" t="n">
-        <v>7428449.646323319</v>
+        <v>7428424</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1454,19 +1392,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1512,15 +1440,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109890404</v>
+        <v>109890405</v>
       </c>
       <c r="B8" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,10 +1480,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>657457.0541060275</v>
+        <v>657434</v>
       </c>
       <c r="R8" t="n">
-        <v>7428424.509115518</v>
+        <v>7428436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1590,19 +1513,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1648,15 +1561,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109890414</v>
+        <v>109890406</v>
       </c>
       <c r="B9" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,10 +1601,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>657602.3044045097</v>
+        <v>657434</v>
       </c>
       <c r="R9" t="n">
-        <v>7428417.201669857</v>
+        <v>7428463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1726,19 +1634,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1784,15 +1682,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109890399</v>
+        <v>109890407</v>
       </c>
       <c r="B10" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1817,16 +1710,7 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1838,10 +1722,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>657625.5164259872</v>
+        <v>657459</v>
       </c>
       <c r="R10" t="n">
-        <v>7428471.621937637</v>
+        <v>7428490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1871,19 +1755,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1929,15 +1803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109890413</v>
+        <v>109890408</v>
       </c>
       <c r="B11" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1974,10 +1843,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>657591.6078764037</v>
+        <v>657511</v>
       </c>
       <c r="R11" t="n">
-        <v>7428452.35751691</v>
+        <v>7428378</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2007,19 +1876,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2065,15 +1924,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109890415</v>
+        <v>109890409</v>
       </c>
       <c r="B12" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2110,10 +1964,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657637.2359562877</v>
+        <v>657523</v>
       </c>
       <c r="R12" t="n">
-        <v>7428418.834219197</v>
+        <v>7428468</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2143,19 +1997,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2201,15 +2045,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109890401</v>
+        <v>109890410</v>
       </c>
       <c r="B13" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2234,16 +2073,7 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2255,10 +2085,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657538.5003134147</v>
+        <v>657547</v>
       </c>
       <c r="R13" t="n">
-        <v>7428404.460445077</v>
+        <v>7428404</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2288,24 +2118,14 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 floral + 1 vegetativ. För sammanlagda antal, se polygonen för hela lokalen</t>
+          <t>För sammanlagda antal, se polygonen för hela lokalen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2349,12 +2169,7 @@
         <v>109890411</v>
       </c>
       <c r="B14" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2391,10 +2206,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>657551.5454069257</v>
+        <v>657551</v>
       </c>
       <c r="R14" t="n">
-        <v>7428389.883800674</v>
+        <v>7428390</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2424,19 +2239,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2482,15 +2287,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109890405</v>
+        <v>109890412</v>
       </c>
       <c r="B15" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2527,10 +2327,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657433.9478744413</v>
+        <v>657552</v>
       </c>
       <c r="R15" t="n">
-        <v>7428436.144314395</v>
+        <v>7428450</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2560,19 +2360,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2618,15 +2408,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109890418</v>
+        <v>109890413</v>
       </c>
       <c r="B16" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,10 +2448,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>657668.575634151</v>
+        <v>657592</v>
       </c>
       <c r="R16" t="n">
-        <v>7428455.248706229</v>
+        <v>7428452</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2696,24 +2481,14 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>För sammanlagda antal, se polygonen för hela lokalen.</t>
+          <t>För sammanlagda antal, se polygonen för hela lokalen</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2754,15 +2529,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109890406</v>
+        <v>109890414</v>
       </c>
       <c r="B17" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2799,10 +2569,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>657433.5585699091</v>
+        <v>657602</v>
       </c>
       <c r="R17" t="n">
-        <v>7428463.248313572</v>
+        <v>7428417</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2832,19 +2602,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2890,15 +2650,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109890410</v>
+        <v>109890415</v>
       </c>
       <c r="B18" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2935,10 +2690,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657547.1522137846</v>
+        <v>657637</v>
       </c>
       <c r="R18" t="n">
-        <v>7428404.568777872</v>
+        <v>7428419</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2968,19 +2723,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3029,12 +2774,7 @@
         <v>109890416</v>
       </c>
       <c r="B19" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3071,10 +2811,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>657637.5668304401</v>
+        <v>657638</v>
       </c>
       <c r="R19" t="n">
-        <v>7428453.843225797</v>
+        <v>7428454</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3104,19 +2844,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3162,15 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109890403</v>
+        <v>109890417</v>
       </c>
       <c r="B20" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3207,10 +2932,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>657428.4733221935</v>
+        <v>657662</v>
       </c>
       <c r="R20" t="n">
-        <v>7428381.180177187</v>
+        <v>7428463</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3240,19 +2965,9 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3298,15 +3013,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109890407</v>
+        <v>109890418</v>
       </c>
       <c r="B21" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3343,10 +3053,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>657459.1921832199</v>
+        <v>657668</v>
       </c>
       <c r="R21" t="n">
-        <v>7428489.500713025</v>
+        <v>7428455</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3376,24 +3086,14 @@
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-04</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>För sammanlagda antal, se polygonen för hela lokalen</t>
+          <t>För sammanlagda antal, se polygonen för hela lokalen.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 388-2026 artfynd.xlsx
+++ b/artfynd/A 388-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -935,6 +945,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,6 +1080,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890401</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1195,6 +1215,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890402</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1316,6 +1341,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890403</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1437,6 +1467,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1558,6 +1593,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1679,6 +1719,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890406</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1800,6 +1845,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890407</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1921,6 +1971,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890408</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2042,6 +2097,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890409</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2163,6 +2223,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890410</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2284,6 +2349,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890411</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2405,6 +2475,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890412</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2526,6 +2601,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890413</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2647,6 +2727,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890414</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2768,6 +2853,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890415</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2889,6 +2979,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890416</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3010,6 +3105,11 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890417</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3131,8 +3231,35 @@
           <t>Inventering av norna</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890418</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>